--- a/documentação/backlog.xlsx
+++ b/documentação/backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Documents\Josué Alvarez\Jach-a-Ajayu\documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC6DAF1-78B3-4C60-9D2D-8EC6DA5B8B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396F0273-5582-4600-803D-80FDA668FB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
   <si>
     <t>Requisito</t>
   </si>
@@ -188,21 +188,6 @@
     <t>Configurar a API Data-Viz para pegar as informações do site e cadastrar no banco de dados</t>
   </si>
   <si>
-    <t>Criar o site com o jogo da memória em HTML, CSS e JavaScript</t>
-  </si>
-  <si>
-    <t>Site Jogo da memória</t>
-  </si>
-  <si>
-    <t>Site Teste de Perfil</t>
-  </si>
-  <si>
-    <t>Criar o site com o teste de perfil em HTML, CSS e JavaScript</t>
-  </si>
-  <si>
-    <t>Desejável</t>
-  </si>
-  <si>
     <t>Semanas</t>
   </si>
   <si>
@@ -228,13 +213,22 @@
   </si>
   <si>
     <t>Desevolver a logo do projeto</t>
+  </si>
+  <si>
+    <t>JACH'A AJAYU</t>
+  </si>
+  <si>
+    <t>Site Quiz Conhecimento das Danças</t>
+  </si>
+  <si>
+    <t>Criar o site de quis com as perguntas sobre as danças da Bolivia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,13 +255,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FFFFD700"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8B0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -282,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -305,12 +312,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFD700"/>
+      <color rgb="FF8B0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -320,6 +340,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>421173</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>984212</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>600075</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D4119EC-E24E-0406-3343-8DA50F5D76D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1030773" y="47626"/>
+          <a:ext cx="563039" cy="552449"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
@@ -621,97 +696,69 @@
     <col min="15" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="K2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="4">
-        <v>8</v>
-      </c>
-      <c r="G2" s="4">
-        <v>2</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="7">
-        <f>SUM(F2:F19)</f>
-        <v>192</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="7">
-        <f>L2</f>
-        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>22</v>
@@ -723,114 +770,127 @@
         <v>8</v>
       </c>
       <c r="G3" s="4">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>56</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H3" s="7"/>
       <c r="I3" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L3" s="7">
-        <f>N2</f>
-        <v>192</v>
+        <f>SUM(F3:F19)</f>
+        <v>169</v>
       </c>
       <c r="M3" s="7">
-        <f>SUMIF(H2:H19,"27/10 - 31/10",F2:F19)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N3" s="7">
-        <f>L3-M3</f>
-        <v>176</v>
+        <f>L3</f>
+        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="I4" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="L4" s="7">
-        <f>L3-48</f>
-        <v>144</v>
-      </c>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+        <f>L3-M3</f>
+        <v>169</v>
+      </c>
+      <c r="M4" s="7">
+        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"27/10 - 31/10")</f>
+        <v>19</v>
+      </c>
+      <c r="N4" s="7">
+        <f>L4-M4</f>
+        <v>150</v>
+      </c>
     </row>
     <row r="5" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4">
         <v>2</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="I5" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L5" s="7">
-        <f t="shared" ref="L5:L7" si="0">L4-48</f>
-        <v>96</v>
-      </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+        <f t="shared" ref="L5:L8" si="0">L4-M4</f>
+        <v>150</v>
+      </c>
+      <c r="M5" s="7">
+        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"03/11 - 07/11")</f>
+        <v>16</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" ref="N5:N7" si="1">L5-M5</f>
+        <v>134</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>34</v>
@@ -839,140 +899,166 @@
         <v>3</v>
       </c>
       <c r="G6" s="4">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="I6" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="L6" s="7">
         <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
+        <v>134</v>
+      </c>
+      <c r="M6" s="7">
+        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"10/11 - 14/11")</f>
+        <v>29</v>
+      </c>
+      <c r="N6" s="7">
+        <f>L6-M6</f>
+        <v>105</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F7" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G7" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I7" s="5" t="b">
         <v>1</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="L7" s="7">
         <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="M7" s="7">
+        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"17/11 - 21/11")</f>
         <v>0</v>
       </c>
-      <c r="M7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>23</v>
+      <c r="N7" s="7">
+        <f>L7-M7</f>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G8" s="4">
         <v>2</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>51</v>
+      </c>
       <c r="I8" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="4">
-        <v>5</v>
-      </c>
       <c r="G9" s="4">
-        <v>3</v>
-      </c>
-      <c r="H9" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>52</v>
+      </c>
       <c r="I9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="7"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="5" t="b">
@@ -982,22 +1068,22 @@
     </row>
     <row r="11" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F11" s="4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G11" s="4">
         <v>2</v>
@@ -1010,25 +1096,25 @@
     </row>
     <row r="12" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F12" s="4">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G12" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="5" t="b">
@@ -1038,22 +1124,22 @@
     </row>
     <row r="13" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F13" s="4">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G13" s="4">
         <v>1</v>
@@ -1062,16 +1148,17 @@
       <c r="I13" s="5" t="b">
         <v>0</v>
       </c>
+      <c r="K13" s="7"/>
     </row>
     <row r="14" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>22</v>
@@ -1085,74 +1172,80 @@
       <c r="G14" s="4">
         <v>1</v>
       </c>
-      <c r="H14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="I14" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15" s="4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G15" s="4">
         <v>1</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="I15" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" s="4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G16" s="4">
         <v>1</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="I16" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
@@ -1173,25 +1266,25 @@
     </row>
     <row r="18" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G18" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="5" t="b">
@@ -1200,7 +1293,7 @@
     </row>
     <row r="19" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>28</v>
@@ -1229,5 +1322,6 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/documentação/backlog.xlsx
+++ b/documentação/backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Documents\Josué Alvarez\Jach-a-Ajayu\documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396F0273-5582-4600-803D-80FDA668FB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6582A087-172E-4637-B715-A56954B51519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Requisito</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>Criar o site de quis com as perguntas sobre as danças da Bolivia</t>
+  </si>
+  <si>
+    <t>Site Minha História</t>
+  </si>
+  <si>
+    <t>Criar o site contando minha história na dança</t>
   </si>
 </sst>
 </file>
@@ -677,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -780,15 +786,15 @@
         <v>55</v>
       </c>
       <c r="L3" s="7">
-        <f>SUM(F3:F19)</f>
-        <v>169</v>
+        <f>SUM(F3:F20)</f>
+        <v>177</v>
       </c>
       <c r="M3" s="7">
         <v>0</v>
       </c>
       <c r="N3" s="7">
         <f>L3</f>
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -824,15 +830,15 @@
       </c>
       <c r="L4" s="7">
         <f>L3-M3</f>
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="M4" s="7">
-        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"27/10 - 31/10")</f>
+        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"27/10 - 31/10")</f>
         <v>19</v>
       </c>
       <c r="N4" s="7">
         <f>L4-M4</f>
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -868,15 +874,15 @@
       </c>
       <c r="L5" s="7">
         <f t="shared" ref="L5:L8" si="0">L4-M4</f>
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="M5" s="7">
-        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"03/11 - 07/11")</f>
+        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"03/11 - 07/11")</f>
         <v>16</v>
       </c>
       <c r="N5" s="7">
-        <f t="shared" ref="N5:N7" si="1">L5-M5</f>
-        <v>134</v>
+        <f t="shared" ref="N5" si="1">L5-M5</f>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -912,15 +918,15 @@
       </c>
       <c r="L6" s="7">
         <f t="shared" si="0"/>
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="M6" s="7">
-        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"10/11 - 14/11")</f>
+        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"10/11 - 14/11")</f>
         <v>29</v>
       </c>
       <c r="N6" s="7">
         <f>L6-M6</f>
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -956,11 +962,11 @@
       </c>
       <c r="L7" s="7">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M7" s="7">
-        <f>SUMIFS(F3:F19,I3:I19,TRUE,H3:H19,"17/11 - 21/11")</f>
-        <v>0</v>
+        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"17/11 - 21/11")</f>
+        <v>8</v>
       </c>
       <c r="N7" s="7">
         <f>L7-M7</f>
@@ -1088,9 +1094,11 @@
       <c r="G11" s="4">
         <v>2</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="I11" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="7"/>
     </row>
@@ -1170,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="G14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>53</v>
@@ -1184,10 +1192,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
@@ -1199,13 +1207,11 @@
         <v>8</v>
       </c>
       <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>53</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H15" s="7"/>
       <c r="I15" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1213,22 +1219,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16" s="4">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>53</v>
@@ -1242,37 +1248,39 @@
         <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" s="4">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G17" s="4">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7"/>
+        <v>2</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>53</v>
+      </c>
       <c r="I17" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>60</v>
+      <c r="B18" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>22</v>
@@ -1295,26 +1303,53 @@
       <c r="A19" s="4">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>28</v>
+      <c r="B19" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>22</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19" s="4">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G19" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>18</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="4">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2</v>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="5" t="b">
         <v>0</v>
       </c>
     </row>

--- a/documentação/backlog.xlsx
+++ b/documentação/backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Documents\Josué Alvarez\Jach-a-Ajayu\documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6582A087-172E-4637-B715-A56954B51519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C4BCF7-096B-4744-9124-FC60064A2AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
   <si>
     <t>Requisito</t>
   </si>
@@ -218,9 +218,6 @@
     <t>JACH'A AJAYU</t>
   </si>
   <si>
-    <t>Site Quiz Conhecimento das Danças</t>
-  </si>
-  <si>
     <t>Criar o site de quis com as perguntas sobre as danças da Bolivia</t>
   </si>
   <si>
@@ -228,12 +225,21 @@
   </si>
   <si>
     <t>Criar o site contando minha história na dança</t>
+  </si>
+  <si>
+    <t>% de Conclusão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Quiz </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="169" formatCode="0.0"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -295,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -324,6 +330,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -696,7 +705,7 @@
     <col min="8" max="8" width="12.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="9.140625" style="3"/>
     <col min="11" max="11" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="3"/>
@@ -966,11 +975,11 @@
       </c>
       <c r="M7" s="7">
         <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"17/11 - 21/11")</f>
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="N7" s="7">
         <f>L7-M7</f>
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1006,7 +1015,7 @@
       </c>
       <c r="L8" s="7">
         <f t="shared" si="0"/>
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="M8" s="7" t="s">
         <v>23</v>
@@ -1066,11 +1075,19 @@
       <c r="G10" s="4">
         <v>3</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="I10" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="11">
+        <f>13/18*100</f>
+        <v>72.222222222222214</v>
+      </c>
     </row>
     <row r="11" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
@@ -1192,10 +1209,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>22</v>
@@ -1209,9 +1226,11 @@
       <c r="G15" s="4">
         <v>2</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>54</v>
+      </c>
       <c r="I15" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1304,10 +1323,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>22</v>
@@ -1323,7 +1342,7 @@
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">

--- a/documentação/backlog.xlsx
+++ b/documentação/backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Documents\Josué Alvarez\Jach-a-Ajayu\documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C4BCF7-096B-4744-9124-FC60064A2AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1C72D8-ECD8-4B95-B160-E47A44849412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
   <si>
     <t>Requisito</t>
   </si>
@@ -215,9 +215,6 @@
     <t>Desevolver a logo do projeto</t>
   </si>
   <si>
-    <t>JACH'A AJAYU</t>
-  </si>
-  <si>
     <t>Criar o site de quis com as perguntas sobre as danças da Bolivia</t>
   </si>
   <si>
@@ -227,20 +224,20 @@
     <t>Criar o site contando minha história na dança</t>
   </si>
   <si>
-    <t>% de Conclusão</t>
-  </si>
-  <si>
     <t xml:space="preserve">Site Quiz </t>
+  </si>
+  <si>
+    <t>Percentual de Conclusão:</t>
+  </si>
+  <si>
+    <t>Jach'a Ajayu - A alma do Folclore Boliviano</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +271,13 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -289,7 +293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -297,53 +301,225 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
           <xfpb:xfComplement i="0"/>
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF8B0000"/>
       <color rgb="FFFFD700"/>
-      <color rgb="FF8B0000"/>
     </mruColors>
   </colors>
   <extLst>
@@ -361,15 +537,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>421173</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>984212</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>600075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -692,687 +868,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="B1:O21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="4"/>
-    <col min="2" max="2" width="31.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="3"/>
-    <col min="7" max="7" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.140625" style="3"/>
-    <col min="11" max="11" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="3"/>
+    <col min="1" max="1" width="1.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="2"/>
+    <col min="3" max="3" width="31.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="1" spans="2:15" ht="9" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:15" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+    </row>
+    <row r="3" spans="2:15" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K3" s="6"/>
+      <c r="L3" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O3" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="13">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D4" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="4">
+      <c r="G4" s="11">
         <v>8</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H4" s="11">
         <v>2</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="5" t="b">
+      <c r="I4" s="11"/>
+      <c r="J4" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L4" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="L3" s="7">
-        <f>SUM(F3:F20)</f>
+      <c r="M4" s="11">
+        <f>SUM(G4:G21)</f>
         <v>177</v>
       </c>
-      <c r="M3" s="7">
+      <c r="N4" s="11">
         <v>0</v>
       </c>
-      <c r="N3" s="7">
-        <f>L3</f>
+      <c r="O4" s="14">
+        <f>M4</f>
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+    <row r="5" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="13">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D5" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="4">
+      <c r="G5" s="11">
         <v>8</v>
       </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="H5" s="11">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="J5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="7">
-        <f>L3-M3</f>
+      <c r="M5" s="11">
+        <f>M4-N4</f>
         <v>177</v>
       </c>
-      <c r="M4" s="7">
-        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"27/10 - 31/10")</f>
+      <c r="N5" s="11">
+        <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"27/10 - 31/10")</f>
         <v>19</v>
       </c>
-      <c r="N4" s="7">
-        <f>L4-M4</f>
+      <c r="O5" s="14">
+        <f>M5-N5</f>
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+    <row r="6" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="13">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C6" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D6" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E6" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F6" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="4">
+      <c r="G6" s="11">
         <v>5</v>
       </c>
-      <c r="G5" s="4">
+      <c r="H6" s="11">
         <v>2</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I6" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="J6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="L5" s="7">
-        <f t="shared" ref="L5:L8" si="0">L4-M4</f>
+      <c r="M6" s="11">
+        <f t="shared" ref="M6:M9" si="0">M5-N5</f>
         <v>158</v>
       </c>
-      <c r="M5" s="7">
-        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"03/11 - 07/11")</f>
+      <c r="N6" s="11">
+        <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"03/11 - 07/11")</f>
         <v>16</v>
       </c>
-      <c r="N5" s="7">
-        <f t="shared" ref="N5" si="1">L5-M5</f>
+      <c r="O6" s="14">
+        <f t="shared" ref="O6" si="1">M6-N6</f>
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+    <row r="7" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D7" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="4">
+      <c r="G7" s="11">
         <v>3</v>
       </c>
-      <c r="G6" s="4">
+      <c r="H7" s="11">
         <v>2</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7" t="s">
+      <c r="J7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="7">
+      <c r="M7" s="11">
         <f t="shared" si="0"/>
         <v>142</v>
       </c>
-      <c r="M6" s="7">
-        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"10/11 - 14/11")</f>
+      <c r="N7" s="11">
+        <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"10/11 - 14/11")</f>
         <v>29</v>
       </c>
-      <c r="N6" s="7">
-        <f>L6-M6</f>
+      <c r="O7" s="14">
+        <f>M7-N7</f>
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+    <row r="8" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D8" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G8" s="11">
         <v>3</v>
       </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="H8" s="11">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7" t="s">
+      <c r="J8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="7">
+      <c r="M8" s="11">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="M7" s="7">
-        <f>SUMIFS(F3:F20,I3:I20,TRUE,H3:H20,"17/11 - 21/11")</f>
+      <c r="N8" s="11">
+        <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"17/11 - 21/11")</f>
+        <v>97</v>
+      </c>
+      <c r="O8" s="14">
+        <f>M8-N8</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="13">
+        <v>6</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="11">
+        <v>8</v>
+      </c>
+      <c r="H9" s="11">
+        <v>2</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="13">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="11">
+        <v>8</v>
+      </c>
+      <c r="H10" s="11">
+        <v>2</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="13">
+        <v>8</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="11">
+        <v>5</v>
+      </c>
+      <c r="H11" s="11">
+        <v>3</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="23"/>
+      <c r="N11" s="24">
+        <f>COUNTIF(J4:J21,TRUE)/18</f>
+        <v>0.88888888888888884</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="13">
+        <v>9</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="11">
+        <v>8</v>
+      </c>
+      <c r="H12" s="11">
+        <v>2</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="13">
+        <v>10</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="11">
+        <v>8</v>
+      </c>
+      <c r="H13" s="11">
+        <v>2</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="13">
+        <v>11</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="11">
         <v>21</v>
       </c>
-      <c r="N7" s="7">
-        <f>L7-M7</f>
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="H14" s="11">
+        <v>1</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J14" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="13">
+        <v>12</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G15" s="11">
         <v>8</v>
       </c>
-      <c r="G8" s="4">
+      <c r="H15" s="11">
         <v>2</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="L8" s="7">
-        <f t="shared" si="0"/>
-        <v>92</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="I15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="13">
+        <v>13</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G16" s="11">
         <v>8</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H16" s="11">
         <v>2</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="I16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J16" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="13">
+        <v>14</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="11">
         <v>8</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="H17" s="11">
+        <v>2</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J17" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="13">
+        <v>15</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="4">
-        <v>5</v>
-      </c>
-      <c r="G10" s="4">
-        <v>3</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="F18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="11">
+        <v>13</v>
+      </c>
+      <c r="H18" s="11">
+        <v>2</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J18" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="13">
+        <v>16</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="11">
+        <v>21</v>
+      </c>
+      <c r="H19" s="11">
+        <v>1</v>
+      </c>
+      <c r="I19" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I10" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L10" s="11">
-        <f>13/18*100</f>
-        <v>72.222222222222214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="J19" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="13">
+        <v>17</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="4">
-        <v>8</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="F20" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="11">
+        <v>21</v>
+      </c>
+      <c r="H20" s="11">
+        <v>1</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="J20" s="12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="15">
+        <v>18</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="16">
+        <v>13</v>
+      </c>
+      <c r="H21" s="16">
         <v>2</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="I21" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" s="7"/>
-    </row>
-    <row r="12" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="4">
-        <v>8</v>
-      </c>
-      <c r="G12" s="4">
-        <v>2</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" s="7"/>
-    </row>
-    <row r="13" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="4">
-        <v>21</v>
-      </c>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="4">
-        <v>8</v>
-      </c>
-      <c r="G14" s="4">
-        <v>2</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="4">
-        <v>8</v>
-      </c>
-      <c r="G15" s="4">
-        <v>2</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I15" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="4">
-        <v>8</v>
-      </c>
-      <c r="G16" s="4">
-        <v>2</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I16" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="4">
-        <v>13</v>
-      </c>
-      <c r="G17" s="4">
-        <v>2</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="4">
-        <v>21</v>
-      </c>
-      <c r="G18" s="4">
-        <v>1</v>
-      </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
-        <v>17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="4">
-        <v>21</v>
-      </c>
-      <c r="G19" s="4">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
-        <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="4">
-        <v>13</v>
-      </c>
-      <c r="G20" s="4">
-        <v>2</v>
-      </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="5" t="b">
-        <v>0</v>
+      <c r="J21" s="18" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="D2:J2"/>
+  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/documentação/backlog.xlsx
+++ b/documentação/backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Documents\Josué Alvarez\Jach-a-Ajayu\documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1C72D8-ECD8-4B95-B160-E47A44849412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B8FEC7-142F-462C-8FE8-C6D6B25844EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="65">
   <si>
     <t>Requisito</t>
   </si>
@@ -500,10 +500,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -966,9 +966,11 @@
       <c r="H4" s="11">
         <v>2</v>
       </c>
-      <c r="I4" s="11"/>
+      <c r="I4" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="J4" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="13" t="s">
         <v>55</v>
@@ -1154,11 +1156,11 @@
       </c>
       <c r="N8" s="11">
         <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"17/11 - 21/11")</f>
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="O8" s="14">
         <f>M8-N8</f>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1194,7 +1196,7 @@
       </c>
       <c r="M9" s="16">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N9" s="16" t="s">
         <v>23</v>
@@ -1260,13 +1262,13 @@
       <c r="J11" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="L11" s="23" t="s">
+      <c r="L11" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="M11" s="23"/>
-      <c r="N11" s="24">
+      <c r="M11" s="24"/>
+      <c r="N11" s="23">
         <f>COUNTIF(J4:J21,TRUE)/18</f>
-        <v>0.88888888888888884</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1321,9 +1323,11 @@
       <c r="H13" s="11">
         <v>2</v>
       </c>
-      <c r="I13" s="11"/>
+      <c r="I13" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="J13" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3"/>
     </row>

--- a/documentação/backlog.xlsx
+++ b/documentação/backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josue\Documents\Josué Alvarez\Jach-a-Ajayu\documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B8FEC7-142F-462C-8FE8-C6D6B25844EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3089CF3C-32CF-40AD-941C-BBFF0E0A9FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="64">
   <si>
     <t>Requisito</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>Essencial</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
   <si>
     <t>GitHub - Atualizado</t>
@@ -237,7 +234,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +274,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFD700"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -428,7 +432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -509,6 +513,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,8 +531,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFD700"/>
       <color rgb="FF8B0000"/>
-      <color rgb="FFFFD700"/>
     </mruColors>
   </colors>
   <extLst>
@@ -531,6 +544,1011 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Gráfico de Burndown</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Backlog - Jach''a Ajayu'!$M$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Planejado</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Backlog - Jach''a Ajayu'!$L$4:$L$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Inicio</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27/10 - 31/10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>03/11 - 07/11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10/11 - 14/11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17/11 - 21/11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Entrega</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Backlog - Jach''a Ajayu'!$M$4:$M$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3E3B-4A8A-9BBC-7771087D1936}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Backlog - Jach''a Ajayu'!$O$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pendente</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Backlog - Jach''a Ajayu'!$L$4:$L$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Inicio</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27/10 - 31/10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>03/11 - 07/11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10/11 - 14/11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17/11 - 21/11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Entrega</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Backlog - Jach''a Ajayu'!$O$4:$O$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>177</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>158</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>113</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3E3B-4A8A-9BBC-7771087D1936}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1322430496"/>
+        <c:axId val="1322431936"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1322430496"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1322431936"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1322431936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1322430496"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,6 +1601,42 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>220807</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>35503</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>346364</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>406112</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{322CE516-E9D9-EA73-1EAF-751655823FD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -893,7 +1947,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
@@ -931,16 +1985,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6"/>
-      <c r="L3" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="8" t="s">
+      <c r="L3" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="28" t="s">
         <v>20</v>
       </c>
     </row>
@@ -952,13 +2006,13 @@
         <v>8</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" s="11">
         <v>8</v>
@@ -967,13 +2021,13 @@
         <v>2</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J4" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L4" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M4" s="11">
         <f>SUM(G4:G21)</f>
@@ -992,16 +2046,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="11">
         <v>8</v>
@@ -1010,13 +2064,13 @@
         <v>1</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M5" s="11">
         <f>M4-N4</f>
@@ -1027,8 +2081,8 @@
         <v>19</v>
       </c>
       <c r="O5" s="14">
-        <f>M5-N5</f>
-        <v>158</v>
+        <f>O4-N4</f>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1036,16 +2090,16 @@
         <v>3</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="11">
         <v>5</v>
@@ -1054,25 +2108,25 @@
         <v>2</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M6" s="11">
-        <f t="shared" ref="M6:M9" si="0">M5-N5</f>
-        <v>158</v>
+        <f>M5-44</f>
+        <v>133</v>
       </c>
       <c r="N6" s="11">
         <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"03/11 - 07/11")</f>
         <v>16</v>
       </c>
       <c r="O6" s="14">
-        <f t="shared" ref="O6" si="1">M6-N6</f>
-        <v>142</v>
+        <f>O5-N5</f>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1080,16 +2134,16 @@
         <v>4</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="11">
         <v>3</v>
@@ -1098,25 +2152,25 @@
         <v>2</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J7" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" si="0"/>
-        <v>142</v>
+        <f t="shared" ref="M7:M8" si="0">M6-44</f>
+        <v>89</v>
       </c>
       <c r="N7" s="11">
         <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"10/11 - 14/11")</f>
         <v>29</v>
       </c>
       <c r="O7" s="14">
-        <f>M7-N7</f>
-        <v>113</v>
+        <f t="shared" ref="O7:O9" si="1">O6-N6</f>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,16 +2178,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G8" s="11">
         <v>3</v>
@@ -1142,25 +2196,25 @@
         <v>1</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J8" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="0"/>
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="N8" s="11">
         <f>SUMIFS(G4:G21,J4:J21,TRUE,I4:I21,"17/11 - 21/11")</f>
         <v>113</v>
       </c>
       <c r="O8" s="14">
-        <f>M8-N8</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1168,16 +2222,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>58</v>
-      </c>
       <c r="E9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="G9" s="11">
         <v>8</v>
@@ -1186,23 +2240,24 @@
         <v>2</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J9" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M9" s="16">
-        <f t="shared" si="0"/>
+        <f>M8-45</f>
         <v>0</v>
       </c>
-      <c r="N9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>23</v>
+      <c r="N9" s="16">
+        <v>0</v>
+      </c>
+      <c r="O9" s="17">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1213,13 +2268,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="G10" s="11">
         <v>8</v>
@@ -1228,7 +2283,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J10" s="12" t="b">
         <v>1</v>
@@ -1242,13 +2297,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="11">
         <v>5</v>
@@ -1257,13 +2312,13 @@
         <v>3</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J11" s="12" t="b">
         <v>1</v>
       </c>
       <c r="L11" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M11" s="24"/>
       <c r="N11" s="23">
@@ -1279,13 +2334,13 @@
         <v>11</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="11">
         <v>8</v>
@@ -1294,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J12" s="12" t="b">
         <v>1</v>
@@ -1309,13 +2364,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" s="11">
         <v>8</v>
@@ -1324,7 +2379,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J13" s="12" t="b">
         <v>1</v>
@@ -1339,13 +2394,13 @@
         <v>13</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G14" s="11">
         <v>21</v>
@@ -1354,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J14" s="12" t="b">
         <v>1</v>
@@ -1369,13 +2424,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" s="11">
         <v>8</v>
@@ -1384,7 +2439,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J15" s="12" t="b">
         <v>1</v>
@@ -1395,16 +2450,16 @@
         <v>13</v>
       </c>
       <c r="C16" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>60</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>61</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" s="11">
         <v>8</v>
@@ -1413,7 +2468,7 @@
         <v>2</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J16" s="12" t="b">
         <v>1</v>
@@ -1427,13 +2482,13 @@
         <v>15</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" s="11">
         <v>8</v>
@@ -1442,7 +2497,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J17" s="12" t="b">
         <v>1</v>
@@ -1456,13 +2511,13 @@
         <v>16</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G18" s="11">
         <v>13</v>
@@ -1471,7 +2526,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J18" s="12" t="b">
         <v>1</v>
@@ -1485,13 +2540,13 @@
         <v>17</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="11">
         <v>21</v>
@@ -1500,7 +2555,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J19" s="12" t="b">
         <v>1</v>
@@ -1511,16 +2566,16 @@
         <v>17</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>22</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" s="11">
         <v>21</v>
@@ -1529,7 +2584,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J20" s="12" t="b">
         <v>1</v>
@@ -1540,16 +2595,16 @@
         <v>18</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>22</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" s="16">
         <v>13</v>
@@ -1558,7 +2613,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J21" s="18" t="b">
         <v>1</v>
